--- a/data/trans_dic/P19C02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C02-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,24; 19,97</t>
+          <t>14,08; 19,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,75; 17,95</t>
+          <t>12,75; 18,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,08; 24,49</t>
+          <t>16,86; 24,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,02; 26,22</t>
+          <t>19,07; 26,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,24; 18,93</t>
+          <t>14,44; 18,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,59; 23,81</t>
+          <t>18,47; 23,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,97; 28,89</t>
+          <t>21,67; 28,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,54; 34,74</t>
+          <t>29,45; 34,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,04; 18,81</t>
+          <t>15,14; 18,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,71; 20,46</t>
+          <t>16,88; 20,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,76; 25,86</t>
+          <t>20,64; 25,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,18; 30,32</t>
+          <t>25,97; 30,35</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,39; 33,52</t>
+          <t>28,14; 33,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,95; 35,64</t>
+          <t>30,88; 35,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,74; 37,47</t>
+          <t>32,69; 37,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,47; 49,78</t>
+          <t>31,63; 49,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,17; 36,68</t>
+          <t>31,32; 36,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,34; 38,11</t>
+          <t>33,26; 38,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,05; 41,59</t>
+          <t>37,12; 42,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,84; 65,02</t>
+          <t>47,06; 65,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,41; 34,13</t>
+          <t>30,38; 34,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,65; 36,26</t>
+          <t>32,64; 36,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,7; 39,02</t>
+          <t>35,51; 38,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,12; 55,78</t>
+          <t>41,13; 54,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,78; 44,83</t>
+          <t>35,36; 44,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,27; 46,27</t>
+          <t>36,49; 46,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,72; 52,03</t>
+          <t>43,11; 52,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,34; 63,35</t>
+          <t>55,36; 63,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,49; 47,84</t>
+          <t>37,83; 47,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,72; 46,69</t>
+          <t>36,43; 46,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,43; 49,67</t>
+          <t>41,22; 50,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,61; 60,37</t>
+          <t>53,58; 60,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,35; 45,43</t>
+          <t>37,92; 44,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,12; 45,18</t>
+          <t>38,11; 45,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,09; 49,49</t>
+          <t>43,35; 49,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,06; 60,59</t>
+          <t>55,14; 60,79</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,9; 30,63</t>
+          <t>26,83; 30,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,93; 31,25</t>
+          <t>27,91; 31,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,14; 36,85</t>
+          <t>32,98; 36,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,9; 47,72</t>
+          <t>32,55; 47,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,54; 30,81</t>
+          <t>27,3; 30,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,6; 33,14</t>
+          <t>29,27; 32,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,36; 39,21</t>
+          <t>35,47; 39,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,75; 58,59</t>
+          <t>46,04; 60,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,57; 30,16</t>
+          <t>27,63; 30,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,08; 31,63</t>
+          <t>29,35; 31,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,81; 37,52</t>
+          <t>34,84; 37,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,82; 50,85</t>
+          <t>41,88; 51,05</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una limpieza de boca (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98165; 137693</t>
+          <t>97033; 136073</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99100; 139501</t>
+          <t>99075; 141043</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78124; 112003</t>
+          <t>77125; 111225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92140; 127037</t>
+          <t>92359; 128709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>136556; 181489</t>
+          <t>138433; 181743</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>209989; 268831</t>
+          <t>208616; 264485</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>140353; 184585</t>
+          <t>138464; 183978</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>213194; 250715</t>
+          <t>212509; 250826</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>247988; 310072</t>
+          <t>249501; 310533</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>318629; 389963</t>
+          <t>321829; 391387</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>227569; 283510</t>
+          <t>226271; 281253</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>315701; 365735</t>
+          <t>313254; 366057</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>373156; 440638</t>
+          <t>369852; 438359</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>522241; 601277</t>
+          <t>521085; 602563</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>555450; 635721</t>
+          <t>554629; 635654</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634849; 1109848</t>
+          <t>705177; 1112896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>427122; 502573</t>
+          <t>429229; 497258</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>530536; 606476</t>
+          <t>529194; 610176</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>633086; 710615</t>
+          <t>634275; 718466</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1029565; 1429156</t>
+          <t>1034319; 1448317</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>816291; 916310</t>
+          <t>815719; 912707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1070468; 1188917</t>
+          <t>1070157; 1180449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1215847; 1328719</t>
+          <t>1209347; 1325466</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1820743; 2469743</t>
+          <t>1821162; 2426135</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>156815; 202162</t>
+          <t>159463; 201307</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>160370; 204567</t>
+          <t>161332; 204734</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>213270; 259732</t>
+          <t>215201; 261108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>349782; 400383</t>
+          <t>349909; 401637</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>153233; 195568</t>
+          <t>154627; 196088</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>155593; 197851</t>
+          <t>154359; 196539</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>205524; 252477</t>
+          <t>209543; 254480</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>349334; 393393</t>
+          <t>349115; 391624</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>329720; 390539</t>
+          <t>326015; 386364</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>330095; 391157</t>
+          <t>329993; 392512</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>434168; 498614</t>
+          <t>436806; 501634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>706725; 777782</t>
+          <t>707751; 780283</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>660275; 751819</t>
+          <t>658676; 746373</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>811790; 908276</t>
+          <t>811352; 914662</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>879364; 977640</t>
+          <t>874958; 979125</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1134340; 1596700</t>
+          <t>1089132; 1588626</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>754103; 843476</t>
+          <t>747514; 844575</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>930761; 1042037</t>
+          <t>920435; 1029653</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1009785; 1119729</t>
+          <t>1012957; 1118197</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1633899; 2092172</t>
+          <t>1644252; 2144563</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1431757; 1566168</t>
+          <t>1434830; 1562899</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1759854; 1914031</t>
+          <t>1775601; 1914304</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1917621; 2066975</t>
+          <t>1919151; 2065912</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2892540; 3517341</t>
+          <t>2897182; 3531425</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C02-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,08; 19,74</t>
+          <t>14,18; 19,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,75; 18,15</t>
+          <t>12,71; 17,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,86; 24,32</t>
+          <t>16,6; 24,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,07; 26,57</t>
+          <t>19,6; 26,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,44; 18,95</t>
+          <t>14,32; 19,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,47; 23,42</t>
+          <t>18,65; 23,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,67; 28,8</t>
+          <t>21,81; 28,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,45; 34,76</t>
+          <t>30,38; 35,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,14; 18,84</t>
+          <t>14,92; 18,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,88; 20,53</t>
+          <t>16,73; 20,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,64; 25,65</t>
+          <t>20,81; 26,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,97; 30,35</t>
+          <t>26,64; 31,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,14; 33,35</t>
+          <t>28,25; 33,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,88; 35,71</t>
+          <t>31,1; 35,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,69; 37,47</t>
+          <t>32,56; 37,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,63; 49,92</t>
+          <t>46,74; 51,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,32; 36,29</t>
+          <t>31,12; 36,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,26; 38,35</t>
+          <t>33,35; 38,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,12; 42,05</t>
+          <t>37,09; 41,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,06; 65,9</t>
+          <t>49,44; 53,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,38; 34,0</t>
+          <t>30,47; 34,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,64; 36,01</t>
+          <t>32,86; 36,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,51; 38,92</t>
+          <t>35,76; 39,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,13; 54,8</t>
+          <t>48,76; 51,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,36; 44,64</t>
+          <t>34,6; 44,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,49; 46,31</t>
+          <t>35,64; 46,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,11; 52,3</t>
+          <t>43,04; 52,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,36; 63,55</t>
+          <t>55,47; 63,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,83; 47,97</t>
+          <t>38,4; 47,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,43; 46,38</t>
+          <t>37,03; 46,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,22; 50,06</t>
+          <t>41,0; 49,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,58; 60,1</t>
+          <t>53,58; 60,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,92; 44,94</t>
+          <t>38,13; 44,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,11; 45,33</t>
+          <t>37,88; 45,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,35; 49,79</t>
+          <t>43,16; 49,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,14; 60,79</t>
+          <t>55,49; 60,98</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,83; 30,41</t>
+          <t>26,88; 30,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,91; 31,47</t>
+          <t>27,76; 31,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,98; 36,9</t>
+          <t>32,97; 36,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,55; 47,48</t>
+          <t>45,26; 49,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,3; 30,85</t>
+          <t>27,48; 30,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,27; 32,75</t>
+          <t>29,34; 32,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,47; 39,15</t>
+          <t>35,24; 39,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,04; 60,05</t>
+          <t>47,03; 50,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,63; 30,1</t>
+          <t>27,61; 30,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,35; 31,64</t>
+          <t>29,2; 31,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,84; 37,5</t>
+          <t>34,92; 37,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,88; 51,05</t>
+          <t>46,73; 49,2</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108659</t>
+          <t>123220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>231220</t>
+          <t>258560</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>339879</t>
+          <t>381780</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97033; 136073</t>
+          <t>97770; 137517</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99075; 141043</t>
+          <t>98787; 138593</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77125; 111225</t>
+          <t>75925; 110182</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92359; 128709</t>
+          <t>105327; 143527</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>138433; 181743</t>
+          <t>137320; 185001</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>208616; 264485</t>
+          <t>210653; 266314</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>138464; 183978</t>
+          <t>139311; 184517</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>212509; 250826</t>
+          <t>238336; 278497</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>249501; 310533</t>
+          <t>245956; 309228</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>321829; 391387</t>
+          <t>319014; 393787</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>226271; 281253</t>
+          <t>228134; 285056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>313254; 366057</t>
+          <t>352136; 410948</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>971618</t>
+          <t>1053711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1176096</t>
+          <t>1090849</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2147715</t>
+          <t>2144560</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>369852; 438359</t>
+          <t>371325; 439067</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>521085; 602563</t>
+          <t>524774; 602843</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>554629; 635654</t>
+          <t>552452; 637314</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>705177; 1112896</t>
+          <t>1002788; 1108275</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>429229; 497258</t>
+          <t>426405; 496667</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>529194; 610176</t>
+          <t>530705; 609489</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>634275; 718466</t>
+          <t>633738; 714479</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1034319; 1448317</t>
+          <t>1043534; 1132296</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>815719; 912707</t>
+          <t>818145; 918871</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1070157; 1180449</t>
+          <t>1077169; 1187254</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1209347; 1325466</t>
+          <t>1217702; 1328124</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1821162; 2426135</t>
+          <t>2075293; 2210112</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>375278</t>
+          <t>418958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>370874</t>
+          <t>412196</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>746153</t>
+          <t>831153</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>159463; 201307</t>
+          <t>156019; 200724</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>161332; 204734</t>
+          <t>157581; 203680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215201; 261108</t>
+          <t>214876; 262186</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>349909; 401637</t>
+          <t>389814; 447015</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>154627; 196088</t>
+          <t>156984; 196087</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>154359; 196539</t>
+          <t>156895; 198565</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>209543; 254480</t>
+          <t>208411; 253199</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>349115; 391624</t>
+          <t>388149; 435856</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>326015; 386364</t>
+          <t>327791; 386761</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>329993; 392512</t>
+          <t>327980; 390821</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>436806; 501634</t>
+          <t>434897; 500882</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>707751; 780283</t>
+          <t>791943; 870300</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1455556</t>
+          <t>1595888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1778190</t>
+          <t>1761604</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3233746</t>
+          <t>3357493</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>658676; 746373</t>
+          <t>659841; 748681</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>811352; 914662</t>
+          <t>806970; 914119</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>874958; 979125</t>
+          <t>874879; 976996</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1089132; 1588626</t>
+          <t>1532267; 1668282</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>747514; 844575</t>
+          <t>752463; 845461</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>920435; 1029653</t>
+          <t>922637; 1034041</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1012957; 1118197</t>
+          <t>1006284; 1117082</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1644252; 2144563</t>
+          <t>1702361; 1813225</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1434830; 1562899</t>
+          <t>1433902; 1560556</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1775601; 1914304</t>
+          <t>1766577; 1919501</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1919151; 2065912</t>
+          <t>1923707; 2068082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2897182; 3531425</t>
+          <t>3273316; 3446709</t>
         </is>
       </c>
     </row>
